--- a/sim/resources/sample/prop.xlsx
+++ b/sim/resources/sample/prop.xlsx
@@ -34,7 +34,7 @@
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="F1" authorId="0">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -56,7 +56,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="0">
+    <comment ref="E1" authorId="0">
       <text>
         <r>
           <rPr>
@@ -83,23 +83,17 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="80">
   <si>
     <t>属性id</t>
   </si>
   <si>
-    <t>组别</t>
-  </si>
-  <si>
     <t>游戏id</t>
   </si>
   <si>
     <t>备注</t>
   </si>
   <si>
-    <t>组内序号</t>
-  </si>
-  <si>
     <t>类型</t>
   </si>
   <si>
@@ -115,15 +109,9 @@
     <t>id</t>
   </si>
   <si>
-    <t>team</t>
-  </si>
-  <si>
     <t>gameType</t>
   </si>
   <si>
-    <t>subIdx</t>
-  </si>
-  <si>
     <t>type</t>
   </si>
   <si>
@@ -154,6 +142,15 @@
     <t>触发jackpot概率提升</t>
   </si>
   <si>
+    <t>自动旋转次数</t>
+  </si>
+  <si>
+    <t>快速旋转</t>
+  </si>
+  <si>
+    <t>5,10030007</t>
+  </si>
+  <si>
     <t>1,10340003</t>
   </si>
   <si>
@@ -184,6 +181,9 @@
     <t>jackpot大奖概率提升</t>
   </si>
   <si>
+    <t>5,10340010</t>
+  </si>
+  <si>
     <t>下注金额增加</t>
   </si>
   <si>
@@ -220,6 +220,9 @@
     <t>金蛇招财模式20倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>5,10350010</t>
+  </si>
+  <si>
     <t>1,10170003_10170004|2,10170005</t>
   </si>
   <si>
@@ -256,6 +259,9 @@
     <t>触发奖池概率提升</t>
   </si>
   <si>
+    <t>5,10170011</t>
+  </si>
+  <si>
     <t>1,10180003</t>
   </si>
   <si>
@@ -280,6 +286,9 @@
     <t>免费模式160倍以上大奖概率提升</t>
   </si>
   <si>
+    <t>5,10180011</t>
+  </si>
+  <si>
     <t>1,10210003</t>
   </si>
   <si>
@@ -311,6 +320,9 @@
   </si>
   <si>
     <t>bonus小游戏40倍以上概率提升</t>
+  </si>
+  <si>
+    <t>5,10210014</t>
   </si>
 </sst>
 </file>
@@ -482,12 +494,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1279,18 +1291,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G61"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="6"/>
+  <dimension ref="A1:E73"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="2" width="15.375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16" style="1" customWidth="1"/>
-    <col min="4" max="4" width="18.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="13.5" style="1" customWidth="1"/>
-    <col min="6" max="7" width="26.875" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="15.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="16" style="1" customWidth="1"/>
+    <col min="3" max="3" width="18.125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="26.875" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1306,980 +1317,923 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="2" t="s">
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="G2" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="E3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+    </row>
+    <row r="5" spans="1:5">
       <c r="A5" s="1">
         <v>10030001</v>
       </c>
       <c r="B5" s="1">
+        <v>100300</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="C5" s="1">
-        <v>100300</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="E5" s="1">
-        <v>1</v>
-      </c>
-      <c r="F5" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1">
         <v>10030002</v>
       </c>
       <c r="B6" s="1">
-        <v>2</v>
-      </c>
-      <c r="C6" s="1">
         <v>100300</v>
       </c>
-      <c r="D6" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="1">
-        <v>1</v>
-      </c>
-      <c r="F6" s="5"/>
-      <c r="G6" s="6" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="C6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" s="5"/>
+      <c r="E6" s="6" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1">
         <v>10030003</v>
       </c>
       <c r="B7" s="1">
-        <v>2</v>
-      </c>
-      <c r="C7" s="1">
         <v>100300</v>
       </c>
-      <c r="D7" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E7" s="1">
-        <v>2</v>
-      </c>
-      <c r="F7" s="5"/>
-      <c r="G7" s="6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="C7" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" s="5"/>
+      <c r="E7" s="6" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1">
         <v>10030004</v>
       </c>
       <c r="B8" s="1">
-        <v>2</v>
-      </c>
-      <c r="C8" s="1">
         <v>100300</v>
       </c>
-      <c r="D8" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="1">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="C8" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1">
         <v>10030005</v>
       </c>
       <c r="B9" s="1">
-        <v>3</v>
-      </c>
-      <c r="C9" s="1">
         <v>100300</v>
       </c>
-      <c r="D9" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="E9" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="C9" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1">
         <v>10030006</v>
       </c>
       <c r="B10" s="1">
-        <v>4</v>
-      </c>
-      <c r="C10" s="1">
         <v>100300</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="C10" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="1">
+        <v>10030007</v>
+      </c>
+      <c r="B11" s="1">
+        <v>100300</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12" s="1">
+        <v>10030008</v>
+      </c>
+      <c r="B12" s="1">
+        <v>100300</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="1">
+        <v>10340001</v>
+      </c>
+      <c r="B13" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D13" s="1">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="1">
+        <v>10340002</v>
+      </c>
+      <c r="B14" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="D14" s="5"/>
+      <c r="E14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="E10" s="1">
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="1">
+        <v>10340003</v>
+      </c>
+      <c r="B15" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="D15" s="5"/>
+      <c r="E15" s="6" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="1">
+        <v>10340004</v>
+      </c>
+      <c r="B16" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="1">
+        <v>10340005</v>
+      </c>
+      <c r="B17" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="1">
+        <v>10340006</v>
+      </c>
+      <c r="B18" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="5"/>
+      <c r="E18" s="6" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="1">
+        <v>10340007</v>
+      </c>
+      <c r="B19" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="D19" s="5"/>
+      <c r="E19" s="6" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="1">
+        <v>10340008</v>
+      </c>
+      <c r="B20" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="1">
+        <v>10340009</v>
+      </c>
+      <c r="B21" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="1">
+        <v>10340010</v>
+      </c>
+      <c r="B22" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="1">
+        <v>10340011</v>
+      </c>
+      <c r="B23" s="1">
+        <v>103400</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="1">
+        <v>10350001</v>
+      </c>
+      <c r="B24" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D24" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="1">
-        <v>10340001</v>
-      </c>
-      <c r="B11" s="1">
+    <row r="25" spans="1:5">
+      <c r="A25" s="1">
+        <v>10350002</v>
+      </c>
+      <c r="B25" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D25" s="5"/>
+      <c r="E25" s="6" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="1">
+        <v>10350003</v>
+      </c>
+      <c r="B26" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="D26" s="5"/>
+      <c r="E26" s="6" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="1">
+        <v>10350004</v>
+      </c>
+      <c r="B27" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="1">
+        <v>10350005</v>
+      </c>
+      <c r="B28" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="1">
+        <v>10350006</v>
+      </c>
+      <c r="B29" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="D29" s="5"/>
+      <c r="E29" s="6" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="1">
+        <v>10350007</v>
+      </c>
+      <c r="B30" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="D30" s="5"/>
+      <c r="E30" s="6" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="1">
+        <v>10350008</v>
+      </c>
+      <c r="B31" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="1">
+        <v>10350009</v>
+      </c>
+      <c r="B32" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="1">
+        <v>10350010</v>
+      </c>
+      <c r="B33" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="1">
+        <v>10350011</v>
+      </c>
+      <c r="B34" s="1">
+        <v>103500</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" s="6" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="1">
+        <v>10170001</v>
+      </c>
+      <c r="B35" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C35" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D35" s="1">
         <v>1</v>
       </c>
-      <c r="C11" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="F11" s="1">
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="1">
+        <v>10170002</v>
+      </c>
+      <c r="B36" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="D36" s="5"/>
+      <c r="E36" s="6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="1">
+        <v>10170003</v>
+      </c>
+      <c r="B37" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="1">
+        <v>10170004</v>
+      </c>
+      <c r="B38" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="1">
+        <v>10170005</v>
+      </c>
+      <c r="B39" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="1">
+        <v>10170006</v>
+      </c>
+      <c r="B40" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="1">
+        <v>10170007</v>
+      </c>
+      <c r="B41" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E41" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="1">
+        <v>10170008</v>
+      </c>
+      <c r="B42" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="1">
+        <v>10170009</v>
+      </c>
+      <c r="B43" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="1">
+        <v>10170010</v>
+      </c>
+      <c r="B44" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="1">
+        <v>10170011</v>
+      </c>
+      <c r="B45" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E45" s="6" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="1">
+        <v>10170012</v>
+      </c>
+      <c r="B46" s="1">
+        <v>101700</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="1">
+        <v>10180001</v>
+      </c>
+      <c r="B47" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C47" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D47" s="1">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="1">
-        <v>10340002</v>
-      </c>
-      <c r="B12" s="1">
-        <v>2</v>
-      </c>
-      <c r="C12" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D12" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="F12" s="5"/>
-      <c r="G12" s="6" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="1">
-        <v>10340003</v>
-      </c>
-      <c r="B13" s="1">
-        <v>2</v>
-      </c>
-      <c r="C13" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="6" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="1">
-        <v>10340004</v>
-      </c>
-      <c r="B14" s="1">
-        <v>2</v>
-      </c>
-      <c r="C14" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D14" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="1">
-        <v>10340005</v>
-      </c>
-      <c r="B15" s="1">
-        <v>2</v>
-      </c>
-      <c r="C15" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D15" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="1">
-        <v>10340006</v>
-      </c>
-      <c r="B16" s="1">
-        <v>3</v>
-      </c>
-      <c r="C16" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D16" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="F16" s="5"/>
-      <c r="G16" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="1">
-        <v>10340007</v>
-      </c>
-      <c r="B17" s="1">
-        <v>3</v>
-      </c>
-      <c r="C17" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="5"/>
-      <c r="G17" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="1">
-        <v>10340008</v>
-      </c>
-      <c r="B18" s="1">
-        <v>3</v>
-      </c>
-      <c r="C18" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D18" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="1">
-        <v>10340009</v>
-      </c>
-      <c r="B19" s="1">
-        <v>4</v>
-      </c>
-      <c r="C19" s="1">
-        <v>103400</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="1">
-        <v>10350001</v>
-      </c>
-      <c r="B20" s="1">
+    <row r="48" spans="1:5">
+      <c r="A48" s="1">
+        <v>10180002</v>
+      </c>
+      <c r="B48" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C48" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5">
+      <c r="A49" s="1">
+        <v>10180003</v>
+      </c>
+      <c r="B49" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C49" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5">
+      <c r="A50" s="1">
+        <v>10180004</v>
+      </c>
+      <c r="B50" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C50" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5">
+      <c r="A51" s="1">
+        <v>10180005</v>
+      </c>
+      <c r="B51" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C51" s="1" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5">
+      <c r="A52" s="1">
+        <v>10180006</v>
+      </c>
+      <c r="B52" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C52" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5">
+      <c r="A53" s="1">
+        <v>10180007</v>
+      </c>
+      <c r="B53" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5">
+      <c r="A54" s="1">
+        <v>10180008</v>
+      </c>
+      <c r="B54" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5">
+      <c r="A55" s="1">
+        <v>10180009</v>
+      </c>
+      <c r="B55" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C55" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5">
+      <c r="A56" s="1">
+        <v>10180010</v>
+      </c>
+      <c r="B56" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C56" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5">
+      <c r="A57" s="1">
+        <v>10180011</v>
+      </c>
+      <c r="B57" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C57" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5">
+      <c r="A58" s="1">
+        <v>10180012</v>
+      </c>
+      <c r="B58" s="1">
+        <v>101800</v>
+      </c>
+      <c r="C58" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E58" s="6" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5">
+      <c r="A59" s="1">
+        <v>10210001</v>
+      </c>
+      <c r="B59" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C59" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D59" s="1">
         <v>1</v>
       </c>
-      <c r="C20" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F20" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="1">
-        <v>10350002</v>
-      </c>
-      <c r="B21" s="1">
-        <v>2</v>
-      </c>
-      <c r="C21" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D21" s="1" t="s">
+    </row>
+    <row r="60" spans="1:5">
+      <c r="A60" s="1">
+        <v>10210002</v>
+      </c>
+      <c r="B60" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C60" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="F21" s="5"/>
-      <c r="G21" s="6" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7">
-      <c r="A22" s="1">
-        <v>10350003</v>
-      </c>
-      <c r="B22" s="1">
-        <v>2</v>
-      </c>
-      <c r="C22" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F22" s="5"/>
-      <c r="G22" s="6" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1">
-        <v>10350004</v>
-      </c>
-      <c r="B23" s="1">
-        <v>2</v>
-      </c>
-      <c r="C23" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
-        <v>10350005</v>
-      </c>
-      <c r="B24" s="1">
-        <v>2</v>
-      </c>
-      <c r="C24" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1">
-        <v>10350006</v>
-      </c>
-      <c r="B25" s="1">
-        <v>3</v>
-      </c>
-      <c r="C25" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="F25" s="5"/>
-      <c r="G25" s="6" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1">
-        <v>10350007</v>
-      </c>
-      <c r="B26" s="1">
-        <v>3</v>
-      </c>
-      <c r="C26" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F26" s="5"/>
-      <c r="G26" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1">
-        <v>10350008</v>
-      </c>
-      <c r="B27" s="1">
-        <v>3</v>
-      </c>
-      <c r="C27" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1">
-        <v>10350009</v>
-      </c>
-      <c r="B28" s="1">
-        <v>4</v>
-      </c>
-      <c r="C28" s="1">
-        <v>103500</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1">
-        <v>10170001</v>
-      </c>
-      <c r="B29" s="1">
-        <v>1</v>
-      </c>
-      <c r="C29" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F29" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1">
-        <v>10170002</v>
-      </c>
-      <c r="B30" s="1">
-        <v>2</v>
-      </c>
-      <c r="C30" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="F30" s="5"/>
-      <c r="G30" s="6" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1">
-        <v>10170003</v>
-      </c>
-      <c r="B31" s="1">
-        <v>2</v>
-      </c>
-      <c r="C31" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1">
-        <v>10170004</v>
-      </c>
-      <c r="B32" s="1">
-        <v>2</v>
-      </c>
-      <c r="C32" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D32" s="1" t="s">
+      <c r="E60" s="7" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5">
+      <c r="A61" s="1">
+        <v>10210003</v>
+      </c>
+      <c r="B61" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C61" s="1" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="1">
-        <v>10170005</v>
-      </c>
-      <c r="B33" s="1">
-        <v>2</v>
-      </c>
-      <c r="C33" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D33" s="1" t="s">
+      <c r="E61" s="7" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5">
+      <c r="A62" s="1">
+        <v>10210004</v>
+      </c>
+      <c r="B62" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C62" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="1">
-        <v>10170006</v>
-      </c>
-      <c r="B34" s="1">
-        <v>3</v>
-      </c>
-      <c r="C34" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D34" s="1" t="s">
+      <c r="E62" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5">
+      <c r="A63" s="1">
+        <v>10210005</v>
+      </c>
+      <c r="B63" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C63" s="1" t="s">
         <v>49</v>
       </c>
-      <c r="G34" s="7" t="s">
+    </row>
+    <row r="64" spans="1:5">
+      <c r="A64" s="1">
+        <v>10210006</v>
+      </c>
+      <c r="B64" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C64" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1">
-        <v>10170007</v>
-      </c>
-      <c r="B35" s="1">
-        <v>3</v>
-      </c>
-      <c r="C35" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="G35" s="7" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="1">
-        <v>10170008</v>
-      </c>
-      <c r="B36" s="1">
-        <v>3</v>
-      </c>
-      <c r="C36" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G36" s="7" t="s">
+      <c r="E64" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5">
+      <c r="A65" s="1">
+        <v>10210007</v>
+      </c>
+      <c r="B65" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C65" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="1">
-        <v>10170009</v>
-      </c>
-      <c r="B37" s="1">
-        <v>3</v>
-      </c>
-      <c r="C37" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="1">
-        <v>10170010</v>
-      </c>
-      <c r="B38" s="1">
-        <v>4</v>
-      </c>
-      <c r="C38" s="1">
-        <v>101700</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="1">
-        <v>10180001</v>
-      </c>
-      <c r="B39" s="1">
-        <v>1</v>
-      </c>
-      <c r="C39" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F39" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="1">
-        <v>10180002</v>
-      </c>
-      <c r="B40" s="1">
-        <v>2</v>
-      </c>
-      <c r="C40" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G40" s="7" t="s">
+      <c r="E65" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5">
+      <c r="A66" s="1">
+        <v>10210008</v>
+      </c>
+      <c r="B66" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C66" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5">
+      <c r="A67" s="1">
+        <v>10210009</v>
+      </c>
+      <c r="B67" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C67" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5">
+      <c r="A68" s="1">
+        <v>10210010</v>
+      </c>
+      <c r="B68" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C68" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="E68" s="7" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5">
+      <c r="A69" s="1">
+        <v>10210011</v>
+      </c>
+      <c r="B69" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C69" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E69" s="7" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5">
+      <c r="A70" s="1">
+        <v>10210012</v>
+      </c>
+      <c r="B70" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C70" s="1" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5">
+      <c r="A71" s="1">
+        <v>10210013</v>
+      </c>
+      <c r="B71" s="1">
+        <v>102100</v>
+      </c>
+      <c r="C71" s="1" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1">
-        <v>10180003</v>
-      </c>
-      <c r="B41" s="1">
-        <v>2</v>
-      </c>
-      <c r="C41" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G41" s="7" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="1">
-        <v>10180004</v>
-      </c>
-      <c r="B42" s="1">
-        <v>2</v>
-      </c>
-      <c r="C42" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G42" s="7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="1">
-        <v>10180005</v>
-      </c>
-      <c r="B43" s="1">
-        <v>2</v>
-      </c>
-      <c r="C43" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="1">
-        <v>10180006</v>
-      </c>
-      <c r="B44" s="1">
-        <v>3</v>
-      </c>
-      <c r="C44" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G44" s="7" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1">
-        <v>10180007</v>
-      </c>
-      <c r="B45" s="1">
-        <v>3</v>
-      </c>
-      <c r="C45" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G45" s="7" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="1">
-        <v>10180008</v>
-      </c>
-      <c r="B46" s="1">
-        <v>3</v>
-      </c>
-      <c r="C46" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G46" s="7" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="1">
-        <v>10180009</v>
-      </c>
-      <c r="B47" s="1">
-        <v>3</v>
-      </c>
-      <c r="C47" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D47" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="1">
-        <v>10180010</v>
-      </c>
-      <c r="B48" s="1">
-        <v>4</v>
-      </c>
-      <c r="C48" s="1">
-        <v>101800</v>
-      </c>
-      <c r="D48" s="1" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7">
-      <c r="A49" s="1">
-        <v>10210001</v>
-      </c>
-      <c r="B49" s="1">
-        <v>1</v>
-      </c>
-      <c r="C49" s="1">
+    <row r="72" spans="1:5">
+      <c r="A72" s="1">
+        <v>10210014</v>
+      </c>
+      <c r="B72" s="1">
         <v>102100</v>
       </c>
-      <c r="D49" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="F49" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7">
-      <c r="A50" s="1">
-        <v>10210002</v>
-      </c>
-      <c r="B50" s="1">
-        <v>2</v>
-      </c>
-      <c r="C50" s="1">
+      <c r="C72" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="73" spans="1:5">
+      <c r="A73" s="1">
+        <v>10210015</v>
+      </c>
+      <c r="B73" s="1">
         <v>102100</v>
       </c>
-      <c r="D50" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="G50" s="7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" s="1">
-        <v>10210003</v>
-      </c>
-      <c r="B51" s="1">
-        <v>2</v>
-      </c>
-      <c r="C51" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="G51" s="7" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" s="1">
-        <v>10210004</v>
-      </c>
-      <c r="B52" s="1">
-        <v>2</v>
-      </c>
-      <c r="C52" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D52" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="G52" s="7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7">
-      <c r="A53" s="1">
-        <v>10210005</v>
-      </c>
-      <c r="B53" s="1">
-        <v>2</v>
-      </c>
-      <c r="C53" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D53" s="1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" s="1">
-        <v>10210006</v>
-      </c>
-      <c r="B54" s="1">
-        <v>3</v>
-      </c>
-      <c r="C54" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D54" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="G54" s="7" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7">
-      <c r="A55" s="1">
-        <v>10210007</v>
-      </c>
-      <c r="B55" s="1">
-        <v>3</v>
-      </c>
-      <c r="C55" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D55" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="G55" s="7" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7">
-      <c r="A56" s="1">
-        <v>10210008</v>
-      </c>
-      <c r="B56" s="1">
-        <v>3</v>
-      </c>
-      <c r="C56" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D56" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="G56" s="7" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7">
-      <c r="A57" s="1">
-        <v>10210009</v>
-      </c>
-      <c r="B57" s="1">
-        <v>3</v>
-      </c>
-      <c r="C57" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D57" s="1" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7">
-      <c r="A58" s="1">
-        <v>10210010</v>
-      </c>
-      <c r="B58" s="1">
-        <v>4</v>
-      </c>
-      <c r="C58" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D58" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="G58" s="7" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7">
-      <c r="A59" s="1">
-        <v>10210011</v>
-      </c>
-      <c r="B59" s="1">
-        <v>4</v>
-      </c>
-      <c r="C59" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D59" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="G59" s="7" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7">
-      <c r="A60" s="1">
-        <v>10210012</v>
-      </c>
-      <c r="B60" s="1">
-        <v>4</v>
-      </c>
-      <c r="C60" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7">
-      <c r="A61" s="1">
-        <v>10210013</v>
-      </c>
-      <c r="B61" s="1">
-        <v>5</v>
-      </c>
-      <c r="C61" s="1">
-        <v>102100</v>
-      </c>
-      <c r="D61" s="1" t="s">
-        <v>56</v>
+      <c r="C73" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" s="6" t="s">
+        <v>79</v>
       </c>
     </row>
   </sheetData>
